--- a/r_table.xlsx
+++ b/r_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM5\S_ENG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42E8BF66-9695-42AB-8D2F-42BD13843902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC037F-3286-41CC-886E-37BE6B7CC9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{460350FA-623F-4F31-945B-D7A7514BBF02}"/>
   </bookViews>
@@ -469,8 +469,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -794,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE0928D8-1AF1-4B59-99CB-4A54325C91C7}">
-  <dimension ref="B1:G8"/>
+  <dimension ref="B1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.3984375" customWidth="1"/>
@@ -806,167 +807,169 @@
     <col min="7" max="7" width="35.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:7" ht="114" x14ac:dyDescent="0.45">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="2:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>